--- a/data_extactor/batch_10_fa/batch_0011_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0011_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Financial Risk Specialists (متخصصان ریسک مالی)</t>
+          <t>متخصصان ریسک مالی (Financial Risk Specialists)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Analyst | Equity Research Analyst | Risk Analyst | Risk Manager | Risk Specialist | Securities Analyst</t>
+          <t>تحلیل‌گر | تحلیل‌گر پژوهش سهام | تحلیل‌گر ریسک | مدیر ریسک | کارشناس ریسک | تحلیل‌گر اوراق بهادار</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | Advanced Portfolio Technologies Report Builder | Advanced Portfolio Technologies Simulator | Amazon Web Services AWS software | Analyse-it | AnalyzerXL | نرم‌افزار تحلیل مستمری‌ها | Apache Hive | Apache Pig | Apple AppleWorks | Apple Keynote | Aptech Systems GAUSS | نرم‌افزار تحلیل فنی Aspen Graphics | Atlassian JIRA | BizBench | BizPricer | Business Forecast Systems Forecast Pro | C++ | Corel QuattroPro | نرم‌افزار بصری‌سازی داده | DealMaven Comparable Company Valuation Analysis | DealMaven M&amp;A Accretion/Dilution One-Pager | DealMaven Modeling ToolPack for Excel | DealMaven PresLink for PowerPoint and Word | Decisioneering Crystal Ball | Delphi Technology | Derivatives Imagine Trading System | Derivicom FinOptions XL | نرم‌افزار پیش‌بینی اقتصادی | Experian Credinomics | Express Business Valuations | Factiva | FileMaker Pro | FinEng Solutions PerfoRM | FinEng Solutions Quantis | نرم‌افزار مدل‌سازی مالی | نرم‌افزار تحلیل الگوی فراکتال | نرم‌افزار حسابداری صندوق | نرم‌افزار بهینه‌سازی الگوریتم ژنتیک | نرم‌افزار الگوریتم ژنتیک | Google Docs | Google Slides | Harland Financial Solutions DecisionPro | نرم‌افزار مدیریت منابع انسانی HRMS | I-flex Solutions Reveleus Investment Performance Measurement | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Lotus Approach | IBM Notes | IBM Power Systems software | IBM SPSS Statistics | Innova Financial Solutions Derivatives Expert | Insightful S-PLUS | Intuit QuickBooks | Ivorix Neurostrategy Finance | Keypoint DataDesk | Leading Market Technologies EXPO | LexisNexis | Linux | Longview Consolidation | Longview Performance Management Platform | Longview Solutions Khalix | نرم‌افزار سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار پیش‌بینی بازار | Marketo Marketing Automation | نرم‌افزار ریاضی | Matheny Pattern Forecaster Plus | McAfee | MergerStat Control Premiums | MergerStat Price to Earnings Ratios | MicroStrategy | Microsoft Access | Microsoft Azure software | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | MoneySoft Corporate Valuation | نرم‌افزار شبیه‌سازی Monte Carlo | Montgomery Investment Technology Bonds XL | Montgomery Investment Technology Exotics XL | Montgomery Investment Technology FinTools | Montgomery Investment Technology Options XL | Montgomery Investment Technology QuoteTools | Montgomery Investment Technology Risk XL | Montgomery Investment Technology SigTools | Montgomery Investment Technology Utility XL | Moss Adams Profit Mentor | نرم‌افزار تحلیل صندوق سرمایه‌گذاری مشترک | NetSuite ERP | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions Trading Solutions | NeuroSolutions for MatLab | OptionVue Options Analysis | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Palisade Bond @nalyst | Palisade Evolver | Palisade StatTools | نرم‌افزار تشخیص الگو | Peer-to-Peer Financial Analysis | Perforce Helix software | Perl | Pi Blue OptWorks Excel | نرم‌افزار مدیریت سبد سهام | نرم‌افزار قیمت‌گذاری | PyTorch | Python | Qlik Tech QlikView | نرم‌افزار مدل‌سازی تخفیف قابلیت بازاریابی QMD | R | نرم‌افزار تولید گزارش | نرم‌افزار گزارش‌گیری | RiskMetrics Group WealthBench | Ruby | S&amp;P Capital IQ | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SSA Global Infinium Financial Management | Sage 50 Accounting | نرم‌افزار Salesforce | نرم‌افزار تحلیل اوراق بهادار | ServiceNow | Spreadware Business Financial Analysis | Spreadware Business Valuator | Spreadware Pro Forma | Standard &amp; Poor's Capital IQ Compustat | StataCorp Stata | Steele Mutual Fund and Variable Annuity Expert | Structured query language SQL | SunGard BancWare | SunGard Kiodex Risk Workbench | Tableau | نرم‌افزار مالیاتی | TechHackers Convertible Bond @nalyst | TechHackers Credit @nalyst | TechHackers Exotic @nalyst | TechHackers Financial @nalyst | TechHackers IRO @nalyst | TechHackers MBS @nalyst | TechHackers Swap @nalyst | TensorFlow | Teradata Database | Tetrahex Fractal Finance | The MathWorks MATLAB | TickQuest NeoTicker | Tips Standard Securities Calculation Bond Analytics Module | Tips Standard Securities Calculation Mortgage-Backed Analytics Module | TradeTools Financial Market Databases | TradeTools Monthly U.S. Economic Database | Trendsetter Software ProAnalyst | UNIX | Unlimited Learning Resources Valusource Pro | ValuSource BIZCOMPS | Ward Systems Group GeneHunter | Ward Systems Group NeuralShell Predictor | Ward Systems Group NeuroShell Trader | نرم‌افزار مرورگر وب | Whitebirch Software Projected Financials | Wolfram Research Derivatives | Wolfram Research Mathematica | Wolfram Research Mathematica Finance Essentials | Wolfram Research Mathematica UnRisk Pricing Engine | نرم‌افزار Yardi | dailyVest Investment Personalization Platform</t>
+          <t>ADP Workforce Now | Advanced Portfolio Technologies Report Builder | Advanced Portfolio Technologies Simulator | نرم‌افزار Amazon Web Services AWS | Analyse-it | AnalyzerXL | نرم‌افزار تحلیل مستمری‌ها | Apache Hive | Apache Pig | Apple AppleWorks | Apple Keynote | Aptech Systems GAUSS | نرم‌افزار تحلیل فنی Aspen Graphics | Atlassian JIRA | BizBench | BizPricer | Business Forecast Systems Forecast Pro | C++ | Corel QuattroPro | نرم‌افزار تجسم داده | DealMaven Comparable Company Valuation Analysis | DealMaven M&amp;A Accretion/Dilution One-Pager | DealMaven Modeling ToolPack for Excel | DealMaven PresLink for PowerPoint and Word | Decisioneering Crystal Ball | Delphi Technology | Derivatives Imagine Trading System | Derivicom FinOptions XL | نرم‌افزار پیش‌بینی اقتصادی | Experian Credinomics | Express Business Valuations | Factiva | FileMaker Pro | FinEng Solutions PerfoRM | FinEng Solutions Quantis | نرم‌افزار مدل‌سازی مالی | نرم‌افزار تحلیل الگوی فراکتال | نرم‌افزار حسابداری صندوق | نرم‌افزار بهینه‌سازی الگوریتم ژنتیک | نرم‌افزار الگوریتم ژنتیک | Google Docs | Google Slides | Harland Financial Solutions DecisionPro | نرم‌افزار مدیریت منابع انسانی HRMS | I-flex Solutions Reveleus Investment Performance Measurement | IBM Cognos Impromptu | IBM Lotus 1-2-3 | IBM Lotus Approach | IBM Notes | نرم‌افزار IBM Power Systems | IBM SPSS Statistics | Innova Financial Solutions Derivatives Expert | Insightful S-PLUS | Intuit QuickBooks | Ivorix Neurostrategy Finance | Keypoint DataDesk | Leading Market Technologies EXPO | LexisNexis | Linux | Longview Consolidation | Longview Performance Management Platform | Longview Solutions Khalix | سیستم‌های اطلاعات مدیریت MIS | نرم‌افزار پیش‌بینی بازار | Marketo Marketing Automation | نرم‌افزار ریاضی | Matheny Pattern Forecaster Plus | McAfee | MergerStat Control Premiums | MergerStat Price to Earnings Ratios | MicroStrategy | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | MoneySoft Corporate Valuation | نرم‌افزار شبیه‌سازی مونت کارلو | Montgomery Investment Technology Bonds XL | Montgomery Investment Technology Exotics XL | Montgomery Investment Technology FinTools | Montgomery Investment Technology Options XL | Montgomery Investment Technology QuoteTools | Montgomery Investment Technology Risk XL | Montgomery Investment Technology SigTools | Montgomery Investment Technology Utility XL | Moss Adams Profit Mentor | نرم‌افزار تحلیل صندوق‌های سرمایه‌گذاری مشترک | NetSuite ERP | نرم‌افزار مدل‌سازی شبکه عصبی | NeuroSolutions Trading Solutions | NeuroSolutions for MatLab | OptionVue Options Analysis | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Palisade Bond @nalyst | Palisade Evolver | Palisade StatTools | نرم‌افزار تشخیص الگو | Peer-to-Peer Financial Analysis | نرم‌افزار Perforce Helix | Perl | Pi Blue OptWorks Excel | نرم‌افزار مدیریت پورتفولیو | نرم‌افزار قیمت‌گذاری | PyTorch | Python | Qlik Tech QlikView | Quantifying marketability discount QMD modeling software | R | نرم‌افزار تولید گزارش | نرم‌افزار گزارش‌دهی | RiskMetrics Group WealthBench | Ruby | S&amp;P Capital IQ | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | نرم‌افزار SAP | SAS | SAS JMP | SSA Global Infinium Financial Management | Sage 50 Accounting | نرم‌افزار Salesforce | نرم‌افزار تحلیل اوراق بهادار | ServiceNow | Spreadware Business Financial Analysis | Spreadware Business Valuator | Spreadware Pro Forma | Standard &amp; Poor's Capital IQ Compustat | StataCorp Stata | Steele Mutual Fund and Variable Annuity Expert | زبان پرس‌وجوی ساختاریافته SQL | SunGard BancWare | SunGard Kiodex Risk Workbench | Tableau | نرم‌افزار مالیاتی | TechHackers Convertible Bond @nalyst | TechHackers Credit @nalyst | TechHackers Exotic @nalyst | TechHackers Financial @nalyst | TechHackers IRO @nalyst | TechHackers MBS @nalyst | TechHackers Swap @nalyst | TensorFlow | Teradata Database | Tetrahex Fractal Finance | The MathWorks MATLAB | TickQuest NeoTicker | Tips Standard Securities Calculation Bond Analytics Module | Tips Standard Securities Calculation Mortgage-Backed Analytics Module | TradeTools Financial Market Databases | TradeTools Monthly U.S. Economic Database | Trendsetter Software ProAnalyst | UNIX | Unlimited Learning Resources Valusource Pro | ValuSource BIZCOMPS | Ward Systems Group GeneHunter | Ward Systems Group NeuralShell Predictor | Ward Systems Group NeuroShell Trader | نرم‌افزار مرورگر وب | Whitebirch Software Projected Financials | Wolfram Research Derivatives | Wolfram Research Mathematica | Wolfram Research Mathematica Finance Essentials | Wolfram Research Mathematica UnRisk Pricing Engine | نرم‌افزار Yardi | dailyVest Investment Personalization Platform</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتن | صحبت کردن | گوش دادن فعال | علوم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | کامپیوتر و الکترونیک | مدیریت و اداره | قانون و دولت | خدمات مشتری و شخصی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | تقسیم زمان | تجسم | حافظه | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران هوش تجاری | مدیران انطباق | تحلیلگران اعتبار | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | تحلیلگران مالی و سرمایه‌گذاری | بیمه‌گران | مدیران صندوق سرمایه‌گذاری | مدیران پیشگیری از زیان | تحلیلگران مدیریت | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | تحلیلگران تحقیق در عملیات | مشاوران مالی شخصی | مدیران امور نظارتی | متخصصان امور نظارتی | متخصصان پیشگیری از زیان خرده‌فروشی | کارگزاران اوراق بهادار، کالا و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | برنامه‌ریزان تداوم کسب‌وکار | تحلیلگران هوش تجاری | مدیران انطباق | تحلیلگران اعتبار | بازرسان مالی | مدیران مالی | تحلیلگران کمی مالی | تحلیلگران مالی و سرمایه‌گذاری | بیمه‌گران | مدیران صندوق سرمایه‌گذاری | مدیران پیشگیری از زیان | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی شخصی | مدیران امور نظارتی | متخصصان امور نظارتی | متخصصان پیشگیری از خسارت خرده‌فروشی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -550,22 +550,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Financial Examiners (بازرسان مالی)</t>
+          <t>بازرسان مالی (Financial Examiners)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bank Examiner | Bank Secrecy Act Anti-Money Laundering Officer (BSA/AML Officer) | Community Reinvestment Act Officer (CRA Officer) | Compliance Analyst | Compliance Specialist | Credit Union Examiner | Credit Union Field Examiner | Examining Officer | Internal Auditor</t>
+          <t>بازرس بانک | مسئول مبارزه با پول‌شویی (BSA/AML) | مسئول قانون سرمایه‌گذاری مجدد در جامعه (CRA) | تحلیل‌گر انطباق | کارشناس انطباق | بازرس اتحادیه اعتباری | بازرس میدانی اتحادیه اعتباری | مأمور بررسی | حسابرس داخلی</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ACL Analytics | نرم‌افزار حسابرسی | نرم‌افزار انطباق مالی | نرم‌افزار تحلیل تراکنش‌های مالی | General Examination System GENESYS | نرم‌افزار مدیریت تحقیقات | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | NILS INSource | ODEN Insurance Services State Rules &amp; Regulations | Oversight Insights On Demand | PricewaterhouseCoopers TeamMate | R | نرم‌افزار SAP | Structured query language SQL | System for Electronic Rate and Form Filing SERFF | Thomson Reuters Westlaw Edge | نرم‌افزار مرورگر وب</t>
+          <t>ACL Analytics | نرم‌افزار حسابرسی | نرم‌افزار انطباق مالی | نرم‌افزار تحلیل تراکنش‌های مالی | General Examination System GENESYS | نرم‌افزار مدیریت تحقیقات | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Windows | Microsoft Word | NILS INSource | ODEN Insurance Services State Rules &amp; Regulations | Oversight Insights On Demand | PricewaterhouseCoopers TeamMate | R | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | System for Electronic Rate and Form Filing SERFF | Thomson Reuters Westlaw Edge | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شنیداری | بیان نوشتاری | حساسیت به مسئله | دید نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | توانایی عددی | سرعت بستار | خلاقیت | روانی ایده‌ها | سرعت ادراکی</t>
+          <t>درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | توانایی عددی | سرعت بستار | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | محیط داخلی، دارای تهویه مطبوع | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارکنان | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارکنان دفتری حسابداری و حسابرسی | تحلیلگران بودجه | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | تحلیلگران اعتبار | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | بازرسان، محققان و تحلیلگران کلاهبرداری | مدیران صندوق سرمایه‌گذاری | مسئولان وام | تحلیلگران مدیریت | مشاوران مالی شخصی | مدیران امنیتی | بازرسان و مأموران جمع‌آوری مالیات | خزانه‌داران و کنترل‌کنندگان</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | مدیران ارشد اجرایی | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | بازرسان، محققان و تحلیلگران کلاهبرداری | مدیران صندوق سرمایه‌گذاری | مسئولان وام | تحلیل‌گران مدیریت | مشاوران مالی شخصی | مدیران امنیتی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | خزانه‌داران و کنترل‌کنندگان</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -607,12 +607,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Credit Counselors (مشاوران اعتبار)</t>
+          <t>مشاوران اعتبار (Credit Counselors)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Accredited Financial Counselor | Certified Consumer Credit and Housing Counselor | Certified Credit Consultant | Certified Credit Counselor | Certified Credit and Housing Counselor | Credit Counselor | Financial Health Counselor | Housing Counselor | Personal Finance Counselor</t>
+          <t>مشاور مالی دارای گواهی صلاحیت | مشاور دارای گواهی اعتبار مصرف‌کننده و مسکن | مشاور اعتباری دارای گواهی صلاحیت | مشاور اعتباری دارای گواهی صلاحیت | مشاور اعتبار و مسکن دارای گواهی صلاحیت | مشاور اعتباری | مشاور سلامت مالی | مشاور مسکن | مشاور مالی شخصی</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | گوش دادن فعال | نوشتن | تفکر انتقادی | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | اقتصاد و حسابداری | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | اقتصاد و حسابداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شنیداری | درک نوشتاری | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | تماس با دیگران | تناوب تصمیم‌گیری | محیط داخلی، دارای تهویه مطبوع | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های مکتوب | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت کار با، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | تعامل با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | ارتباط با دیگران | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | جمع‌آوری‌کنندگان صورت‌حساب و حساب | کارکنان دفتری حسابداری و حسابرسی | مددکاران اجتماعی کودک، خانواده و مدرسه | تحلیلگران اعتبار | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | نمایندگان خدمات مشتری | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارکنان دفتری پردازش ادعا و سیاست بیمه | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارکنان دفتری وام | مسئولان وام | کارکنان دفتری حساب‌های جدید | مشاوران مالی شخصی | مشاوران توانبخشی | کارگزاران اوراق بهادار، کالا و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات | تهیه‌کنندگان اظهارنامه مالیاتی</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان دفترداری، حسابداری و حسابرسی | مددکاران اجتماعی کودک، خانواده و مدرسه | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | مشاوران توانبخشی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -664,22 +664,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loan Officers (مسئولان وام)</t>
+          <t>مسئولان وام (Loan Officers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Commercial Banker | Commercial Loan Officer | Corporate Banking Officer | Financial Aid Advisor | Financial Aid Counselor | Financial Aid Officer | Financial Counselor | Loan Counselor | Loan Officer | Mortgage Loan Officer</t>
+          <t>بانکدار تجاری | مسئول تسهیلات تجاری | مسئول بانکداری شرکتی | مشاور کمک‌هزینه تحصیلی | مشاور کمک‌هزینه تحصیلی | مسئول کمک‌هزینه تحصیلی | مشاور مالی | مشاور تسهیلات | مسئول تسهیلات | مسئول تسهیلات رهنی</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1003 Uniform Residential Loan Application | نرم‌افزار وام اقساطی | Bankers Systems Rembrandt Lending System | Bottom Line LoanMaster Loan Servicing | CGI-AMS BureauLink Enterprise | CGI-AMS CACS Enterprise | CGI-AMS Strata | California Infinite LPS | Calyx Point | Click1003 Online Mortgage Application | زبان برنامه‌نویسی COBOL | نرم‌افزار تحلیل اعتبار و ریسک | نرم‌افزار تشخیص کلاهبرداری اعتباری | نرم‌افزار پذیره‌نویسی اعتبار | Customer information control system CICS | Datatel Colleague | Delphi Discovery | Dun and Bradstreet Global DecisionMaker | Dynamic Loanledger | EDExpress | ELM Resources ELM | EMT Applications CounselorMax | Ellie Mae Contour | Ellie Mae Genesis | Equifax Advanced Decisioning | Equifax Application Engine | Equifax InterConnect | Experian Credinomics | Experian Detect | Experian FraudShield | Experian Quest | Experian Retention Triggers | Experian Strategy Management | Experian Transact SM | FAS Loan Service Plus | Fair Isaac Application Risk Model Software | Fair Isaac Capstone Decision Manager | Fair Isaac Falcon ID | Fannie Mae Desktop Underwriter | FileMaker Pro | Financial Industry Computer Systems Loan Accountant | Financial Industry Computer Systems Loan Originator | Financial Industry Computer Systems Loan Producer | سیستم مدیریت کمک مالی FAM | Freddie Mac Loan Prospector | Harland Financial Solutions DecisionPro | Harland Interlinq MortgageWare | IA Systems StreamLend | IBM Notes | Indus Lending Solutions | Integra Destiny Loan Origination | LA PRO Loan Administrator Pro | LexisNexis | نرم‌افزار پردازش درخواست وام | نرم‌افزار ایجاد وام | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moody's KMV CreditEdge | Moody's KMV Decisions | Moody's KMV Financial Analyst | Moody's KMV Risk Advisor | Moody's KMV Risk Analyst | سیستم مدیریت فرصت OMS | Oracle PeopleSoft | Plimus Loan Artist | QuikDraw Loan Management System | RealBenefits Amortization Loan | نرم‌افزار SAP | نرم‌افزار سیستم‌های اطلاعات دانشجویی SIS | SunGard Higher Education Banner Financial Aid | Sungard Higher Education PowerFAIDS | نرم‌افزار مالیاتی | Technicost LOS | The Mortgage Office Loan Origination | The Mortgage Office Loan Servicing | VueCentric MortgageDashboard | نرم‌افزار مرورگر وب | White Clarke North America Credit Adjudication and Lending Management | Wolters Kluwer Financial Services ComplianceOne | Zoom | eCredit Enterprise | eOriginal eCore Business Suite</t>
+          <t>1003 Uniform Residential Loan Application | نرم‌افزار وام اقساطی | Bankers Systems Rembrandt Lending System | Bottom Line LoanMaster Loan Servicing | CGI-AMS BureauLink Enterprise | CGI-AMS CACS Enterprise | CGI-AMS Strata | California Infinite LPS | Calyx Point | Click1003 Online Mortgage Application | زبان مشترک تجاری COBOL | نرم‌افزار تحلیل اعتبار و ریسک | نرم‌افزار تشخیص تقلب اعتبار | نرم‌افزار پذیره‌نویسی اعتبار | سیستم کنترل اطلاعات مشتری CICS | Datatel Colleague | Delphi Discovery | Dun and Bradstreet Global DecisionMaker | Dynamic Loanledger | EDExpress | ELM Resources ELM | EMT Applications CounselorMax | Ellie Mae Contour | Ellie Mae Genesis | Equifax Advanced Decisioning | Equifax Application Engine | Equifax InterConnect | Experian Credinomics | Experian Detect | Experian FraudShield | Experian Quest | Experian Retention Triggers | Experian Strategy Management | Experian Transact SM | FAS Loan Service Plus | نرم‌افزار مدل ریسک کاربرد Fair Isaac | Fair Isaac Capstone Decision Manager | Fair Isaac Falcon ID | Fannie Mae Desktop Underwriter | FileMaker Pro | Financial Industry Computer Systems Loan Accountant | Financial Industry Computer Systems Loan Originator | Financial Industry Computer Systems Loan Producer | سیستم مدیریت کمک مالی FAM | Freddie Mac Loan Prospector | Harland Financial Solutions DecisionPro | Harland Interlinq MortgageWare | IA Systems StreamLend | IBM Notes | Indus Lending Solutions | Integra Destiny Loan Origination | LA PRO Loan Administrator Pro | LexisNexis | نرم‌افزار پردازش درخواست وام | نرم‌افزار ایجاد وام | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | Moody's KMV CreditEdge | Moody's KMV Decisions | Moody's KMV Financial Analyst | Moody's KMV Risk Advisor | Moody's KMV Risk Analyst | سیستم مدیریت فرصت OMS | Oracle PeopleSoft | Plimus Loan Artist | QuikDraw Loan Management System | RealBenefits Amortization Loan | نرم‌افزار SAP | نرم‌افزار سیستم‌های اطلاعات دانش‌آموزی SIS | SunGard Higher Education Banner Financial Aid | Sungard Higher Education PowerFAIDS | نرم‌افزار مالیاتی | Technicost LOS | The Mortgage Office Loan Origination | The Mortgage Office Loan Servicing | VueCentric MortgageDashboard | نرم‌افزار مرورگر وب | White Clarke North America Credit Adjudication and Lending Management | Wolters Kluwer Financial Services ComplianceOne | Zoom | eCredit Enterprise | eOriginal eCore Business Suite</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نوشتن | ریاضیات | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | دید نزدیک | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | نظم‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای تهویه مطبوع | ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | تناوب تصمیم‌گیری | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های مکتوب | فشار زمانی | سطح رقابت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | فراوانی تصمیم‌گیری | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | جمع‌آوری‌کنندگان صورت‌حساب و حساب | کارکنان دفتری حسابداری و حسابرسی | کارکنان دفتری کارگزاری | تحلیلگران اعتبار | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | مشاوران اعتبار | بازرسان مالی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارکنان دفتری پردازش ادعا و سیاست بیمه | نمایندگان فروش بیمه | بیمه‌گران | مصاحبه‌کنندگان و کارکنان دفتری وام | کارکنان دفتری حساب‌های جدید | مشاوران مالی شخصی | کارگزاران املاک | کارگزاران اوراق بهادار، کالا و خدمات مالی | تهیه‌کنندگان اظهارنامه مالیاتی | متصدیان بانکی</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | بازرسان مالی | مدیران مالی | تحلیلگران مالی و سرمایه‌گذاری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | بیمه‌گران | مصاحبه‌کنندگان و کارمندان وام | کارمندان حساب‌های جدید | مشاوران مالی شخصی | کارگزاران املاک | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | تهیه‌کنندگان اظهارنامه مالیاتی | تحویل‌داران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tax Examiners and Collectors, and Revenue Agents (بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد)</t>
+          <t>بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد (Tax Examiners and Collectors, and Revenue Agents)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>City Tax Auditor | Collections Specialist | Revenue Agent | Revenue Collector | Revenue Officer | Revenue Specialist | Tax Collector | Tax Compliance Officer | Tax Examiner | Tax Examining Technician</t>
+          <t>حسابرس مالیاتی شهرداری | متخصص مجموعه‌ها | مأمور وصول درآمد | وصول‌کننده درآمد | مسئول درآمد | کارشناس درآمد | مأمور وصول مالیات | مسئول انطباق مالیاتی | بازرس مالیاتی | تکنسین بررسی مالیاتی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ADP Workforce Now | نرم‌افزار Alteryx | نرم‌افزار سیستم مالیاتی خودکار | نرم‌افزار سیستم مدیریت اسناد | نرم‌افزار ایمیل | نرم‌افزار حسابداری صندوق | سیستم‌های پردازش تصویر | Intuit QuickBooks | Intuit TurboTax | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده آنلاین | نرم‌افزار تشخیص نوری کاراکتر OCR | نرم‌افزار SAP | نرم‌افزار مدیریت مالیات بر دارایی انطباق مالیاتی | نرم‌افزار مالیاتی | نرم‌افزار مرورگر وب</t>
+          <t>ADP Workforce Now | نرم‌افزار Alteryx | نرم‌افزار سیستم مالیاتی خودکار | نرم‌افزار سیستم مدیریت اسناد | نرم‌افزار ایمیل | نرم‌افزار حسابداری صندوق | سیستم‌های پردازش تصویر | Intuit QuickBooks | Intuit TurboTax | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده آنلاین | نرم‌افزار تشخیص نوری کاراکتر OCR | نرم‌افزار SAP | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>صحبت کردن | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نوشتن | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | وضوح گفتار | بیان نوشتاری | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | ایمیل | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف مشابه | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | تناوب تصمیم‌گیری | نامه‌ها و یادداشت‌های مکتوب | فشار زمانی | تعامل با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>اهمیت دقیق یا درست بودن | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | فشار زمانی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | جمع‌آوری‌کنندگان صورت‌حساب و حساب | کارکنان دفتری صورت‌حساب و ثبت | کارکنان دفتری حسابداری و حسابرسی | تحلیلگران بودجه | تنظیم‌کنندگان، بازرسان و محققان ادعا | مسئولان انطباق | کارکنان دفتری مکاتبات | کارکنان دفتری دادگاه، شهرداری و مجوز | تحلیلگران اعتبار | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | مشاوران اعتبار | نمایندگان خدمات مشتری | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | کارکنان دفتری پردازش ادعا و سیاست بیمه | مسئولان وام | کارکنان دفتری حقوق و دستمزد و زمان‌سنجی | مشاوران مالی شخصی | تهیه‌کنندگان اظهارنامه مالیاتی</t>
+          <t>حسابداران و حسابرسان | وصول‌کنندگان قبوض و حساب‌ها | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران بودجه | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | افسران انطباق | کارمندان مکاتبات | کارمندان دادگاه، شهرداری و مجوز | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | کارمندان پردازش بیمه و بیمه‌نامه | مسئولان وام | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | تهیه‌کنندگان اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -778,42 +778,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tax Preparers (تهیه‌کنندگان اظهارنامه مالیاتی)</t>
+          <t>تهیه‌کنندگان اظهارنامه مالیاتی (Tax Preparers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CPA (Certified Public Accountant) | Enrolled Agent | Income Tax Preparer | Tax Accountant | Tax Advisor | Tax Associate | Tax Consultant | Tax Preparer | Tax Professional | Tax Specialist</t>
+          <t>CPA (حسابدار رسمی) | نماینده مالیاتی دارای پروانه | تنظیم‌کننده اظهارنامه مالیات بر درآمد | حسابدار مالیاتی | مشاور مالیاتی | کارشناس مالیاتی | مشاور مالیاتی | تنظیم‌کننده اظهارنامه مالیاتی | متخصص امور مالیاتی | کارشناس مالیاتی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ACI TaskTracker | ATX Total Accounting Office | ATX Total Tax Office | CCH ProSystem fx TAX | Creative Solutions CPA Depreciation | Creative Solutions UltraTax CS | Datagroup ElectroFile 1040 | Datagroup ElectroFile ELF | Datagroup ElectroFile ST | Datair Employee Benefits Systems | Electronic ToolKit for Tax Preparers | نرم‌افزار ایمیل | ExacTax PackageEX | GreatTax | Greatland Corporation Winfiler | نرم‌افزار راه‌حل‌های مالی Intellitax | Intuit ProSeries | Intuit QuickBooks | Intuit TurboTax | Kleinrock Publishing | LaCerte 1040 Tax Analyzer | Laserfiche Avante | M8 Client Billing | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Petz Enterprises V-Tax | Quicken | Sage 50 Accounting | Sales Tax Tools Sales Tax Researcher | ScheduleVIEW | Sungard Relius | Sync Essentials Trade Accountant | نرم‌افزار مدیریت مالیات بر دارایی انطباق مالیاتی | نرم‌افزار مالیاتی | Thomson GoSystem MyTaxInfo | Thomson Reuters UltraTax CS | Universal Tax Systems TaxWise</t>
+          <t>ACI TaskTracker | ATX Total Accounting Office | ATX Total Tax Office | CCH ProSystem fx TAX | Creative Solutions CPA Depreciation | Creative Solutions UltraTax CS | Datagroup ElectroFile 1040 | Datagroup ElectroFile ELF | Datagroup ElectroFile ST | Datair Employee Benefits Systems | Electronic ToolKit for Tax Preparers | نرم‌افزار ایمیل | ExacTax PackageEX | GreatTax | Greatland Corporation Winfiler | Intellitax financial solutions software | Intuit ProSeries | Intuit QuickBooks | Intuit TurboTax | Kleinrock Publishing | LaCerte 1040 Tax Analyzer | Laserfiche Avante | M8 Client Billing | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Word | Petz Enterprises V-Tax | Quicken | Sage 50 Accounting | Sales Tax Tools Sales Tax Researcher | ScheduleVIEW | Sungard Relius | Sync Essentials Trade Accountant | نرم‌افزار مدیریت مالیات بر دارایی | نرم‌افزار مالیاتی | Thomson GoSystem MyTaxInfo | Thomson Reuters UltraTax CS | Universal Tax Systems TaxWise</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | صحبت کردن | یادگیری فعال | نظارت | ریاضیات | نوشتن</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | کامپیوتر و الکترونیک | اداری</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | دید نزدیک | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | توانایی عددی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بیان نوشتاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | توانایی عددی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | ایمیل | مکالمات تلفنی | اهمیت تکرار وظایف مشابه | بحث‌های حضوری با افراد و درون تیم‌ها | فشار زمانی | تماس با دیگران | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | تناوب تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | ایمیل | مکالمات تلفنی | اهمیت تکرار وظایف یکسان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | ارتباط با دیگران | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارکنان دفتری صورت‌حساب و ثبت | کارکنان دفتری حسابداری و حسابرسی | کارکنان دفتری کارگزاری | تحلیلگران بودجه | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | مشاوران اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارکنان دفتری پردازش ادعا و سیاست بیمه | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان و کارکنان دفتری وام | مسئولان وام | دستیاران حقوقی و وکلا | کارکنان دفتری حقوق و دستمزد و زمان‌سنجی | مشاوران مالی شخصی | بازرسان و مأموران جمع‌آوری مالیات</t>
+          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیلگران بودجه | متخصصان جبران خدمات، مزایا و تحلیل شغل | تحلیلگران اعتبار | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | مشاوران اعتبار | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان مالی | مدیران مالی | کارمندان پردازش بیمه و بیمه‌نامه | منشی‌های حقوقی و دستیاران اداری | مصاحبه‌کنندگان و کارمندان وام | مسئولان وام | پارالیگال‌ها و دستیاران حقوقی | کارمندان حقوق و دستمزد و ثبت زمان | مشاوران مالی شخصی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Financial Specialists, All Other (متخصصان مالی، سایر)</t>
+          <t>متخصصان مالی، سایر (Financial Specialists, All Other)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Analyst | Financial Consultant | Financial Operations Specialist | Financial Planning Analyst | Financial Specialist | Investment Analyst | Portfolio Analyst | Risk Analyst | Securities Analyst | Treasury Analyst</t>
+          <t>تحلیل‌گر مالی | مشاور مالی | کارشناس عملیات مالی | تحلیل‌گر برنامه‌ریزی مالی | کارشناس مالی | تحلیل‌گر سرمایه‌گذاری | تحلیل‌گر سبد سرمایه‌گذاری | تحلیل‌گر ریسک | تحلیل‌گر اوراق بهادار | تحلیل‌گر خزانه‌داری</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Structured query language SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | نرم‌افزار پایگاه داده | Microsoft Word | نرم‌افزار ایمیل | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | Microsoft SharePoint | نرم‌افزار مرورگر وب | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه گسترده | Adobe Acrobat</t>
+          <t>Microsoft Excel | زبان پرس‌وجوی ساختاریافته SQL | Python | R | SAS | IBM SPSS Statistics | Tableau | Microsoft Power BI | Minitab | The MathWorks MATLAB | Oracle Database | Microsoft Access | نرم‌افزار پایگاه داده | Microsoft Word | نرم‌افزار ایمیل | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | Microsoft SharePoint | نرم‌افزار مرورگر وب | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتن | صحبت کردن | گوش دادن فعال | علوم | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | کامپیوتر و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی | پرسنل و منابع انسانی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | تقسیم زمان | تجسم | حافظه | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | صرف زمان برای نشستن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تحلیلگران کمی مالی | بازرسان، محققان و تحلیلگران کلاهبرداری | تحلیلگران مالی و سرمایه‌گذاری | مشاوران مالی شخصی | متخصصان ریسک مالی | تحلیلگران بودجه | تحلیلگران اعتبار | بیمه‌گران | بازرسان مالی | مشاوران اعتبار | مسئولان وام | بازرسان و مأموران جمع‌آوری مالیات | تهیه‌کنندگان اظهارنامه مالیاتی | حسابداران و حسابرسان | ارزیابان و کارشناسان املاک | ارزیابان اموال شخصی و تجاری | مدیران مالی | خزانه‌داران و کنترل‌کنندگان | مدیران صندوق سرمایه‌گذاری | تحلیلگران مدیریت</t>
+          <t>تحلیلگران کمی مالی | بازرسان، محققان و تحلیلگران کلاهبرداری | تحلیلگران مالی و سرمایه‌گذاری | مشاوران مالی شخصی | متخصصان ریسک مالی | تحلیلگران بودجه | تحلیلگران اعتبار | بیمه‌گران | بازرسان مالی | مشاوران اعتبار | مسئولان وام | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | تهیه‌کنندگان اظهارنامه مالیاتی | حسابداران و حسابرسان | ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | مدیران مالی | خزانه‌داران و کنترل‌کنندگان | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -892,42 +892,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Financial Quantitative Analysts (تحلیلگران کمی مالی)</t>
+          <t>تحلیلگران کمی مالی (Financial Quantitative Analysts)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Investment Portfolio Control Consultant | Investment Strategist | Portfolio Manager | Quantitative Analyst | Quantitative Equity Analyst | Quantitative Research Analyst | Quantitative Strategy Analyst | Research Analyst</t>
+          <t>مشاور کنترل سبد سرمایه‌گذاری | راهبردپرداز سرمایه‌گذاری | مدیر پورتفوی | تحلیل‌گر کمّی | تحلیل‌گر کمّی سهام | تحلیل‌گر پژوهش کمّی | تحلیل‌گر راهبرد کمّی | تحلیل‌گر پژوهش</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amazon Web Services AWS software | Apache Hive | Bloomberg Professional | C# | C++ | IBM Cognos Business Intelligence | IBM SPSS Statistics | Insightful S-PLUS | JavaScript | Linux | MicroStrategy | MicroStrategy Desktop | Microsoft Access | Microsoft Azure software | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Oracle JD Edwards EnterpriseOne | Oracle Java | Perl | Python | R | SAS | StataCorp Stata | Structured query language SQL | Tableau | The MathWorks MATLAB | UNIX | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار Amazon Web Services AWS | Apache Hive | Bloomberg Professional | C# | C++ | IBM Cognos Business Intelligence | IBM SPSS Statistics | Insightful S-PLUS | JavaScript | Linux | MicroStrategy | MicroStrategy Desktop | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Power BI | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Oracle JD Edwards EnterpriseOne | Oracle Java | Perl | Python | R | SAS | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | UNIX | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | صحبت کردن | نوشتن | نظارت | استراتژی‌های یادگیری</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ریاضیات | اقتصاد و حسابداری | کامپیوتر و الکترونیک | زبان انگلیسی</t>
+          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک نوشتاری | درک شنیداری | بیان نوشتاری | استدلال قیاسی | توانایی عددی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | نظم‌دهی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | خلاقیت</t>
+          <t>استدلال ریاضی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | توانایی عددی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان برای نشستن | سطح رقابت | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای تهویه مطبوع | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | تماس با دیگران</t>
+          <t>ایمیل | صرف زمان برای نشستن | سطح رقابت | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فشار زمانی | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اکچوئرها | متخصصان آمار زیستی | تحلیلگران هوش تجاری | تحلیلگران سیستم‌های کامپیوتری | تحلیلگران اعتبار | دانشمندان داده | متخصصان انبار داده | معماران پایگاه داده | اقتصاددانان | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مدیران صندوق سرمایه‌گذاری | تحلیلگران مدیریت | تحلیلگران تحقیقات بازار و متخصصان بازاریابی | تحلیلگران تحقیق در عملیات | تست‌کنندگان نفوذ | مشاوران مالی شخصی | کارگزاران اوراق بهادار، کالا و خدمات مالی | دستیاران آماری | آمارشناسان</t>
+          <t>کارشناسان آمار بیمه (اکچوئری) | آمارشناسان زیستی | تحلیلگران هوش تجاری | تحلیلگران سیستم‌های کامپیوتری | تحلیلگران اعتبار | دانشمندان داده | متخصصان انبارش داده | معماران پایگاه داده | اقتصاددانان | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان آزمون نفوذ | مشاوران مالی شخصی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fraud Examiners, Investigators and Analysts (بازرسان، محققان و تحلیلگران کلاهبرداری)</t>
+          <t>بازرسان، محققان و تحلیلگران کلاهبرداری (Fraud Examiners, Investigators and Analysts)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Anti-Fraud Operations Analyst | Casino Gaming Regulator | Certified Fraud Examiner (CFE) | Confidential Investigator | Financial Crimes Investigator | Financial Investigator | Forensic Accountant | Fraud Analyst | Investigator | Special Investigations Unit Investigator (SIU Investigator)</t>
+          <t>تحلیل‌گر عملیات مقابله با تقلب | ناظر مقررات بازی‌های کازینو | بازرس تقلب دارای گواهی صلاحیت (CFE) | بازرس محرمانه | بازرس جرایم مالی | بازرس مالی | حسابدار قضایی | تحلیل‌گر تقلب | بازرس | بازرس واحد تحقیقات ویژه (SIU)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ArcSight Enterprise Threat and Risk Management | نرم‌افزار حسابداری | نرم‌افزار هوش تجاری | نرم‌افزار پرونده الکترونیک سلامت EHR | Guardian Analytics FraudMAP | IBM Cognos | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | PCG Software Virtual Examiner | Python | R | SAP Business Objects | SAS | Splunk Enterprise | Structured query language SQL | TIBCO Spotfire | Tableau | TriZetto QNXT | Vertafore ImageRight</t>
+          <t>ArcSight Enterprise Threat and Risk Management | نرم‌افزار حسابداری | نرم‌افزار هوش تجاری | نرم‌افزار پرونده الکترونیک سلامت EHR | Guardian Analytics FraudMAP | IBM Cognos | LexisNexis | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | نرم‌افزار امنیت سایبری NortonLifeLock | PCG Software Virtual Examiner | Python | R | SAP Business Objects | SAS | Splunk Enterprise | زبان پرس‌وجوی ساختاریافته SQL | TIBCO Spotfire | Tableau | TriZetto QNXT | Vertafore ImageRight</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نوشتن | تفکر انتقادی | صحبت کردن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | کامپیوتر و الکترونیک | مدیریت و اداره | ریاضیات | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | درک شنیداری | حساسیت به مسئله | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | دید نزدیک | نظم‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | خلاقیت | روانی ایده‌ها</t>
+          <t>بیان کتبی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | تناوب تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های حضوری با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | تماس با دیگران | آزادی در تصمیم‌گیری | فشار زمانی | محیط داخلی، دارای تهویه مطبوع | نامه‌ها و یادداشت‌های مکتوب | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف مشابه | نتایج کاری و خروجی‌های سایر کارکنان</t>
+          <t>ایمیل | مکالمات تلفنی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تنظیم‌کنندگان، بازرسان و محققان ادعا | مدیران انطباق | تأییدکنندگان، بررسی‌کنندگان و کارکنان دفتری اعتبار | کارآگاهان و محققان جنایی | تحلیلگران پزشکی قانونی دیجیتال | بازرسان مالی | متخصصان ریسک مالی | تحلیلگران امنیت اطلاعات | تحلیلگران اطلاعات | وکلا | مدیران پیشگیری از زیان | تحلیلگران مدیریت | دستیاران حقوقی و وکلا | مأموران شناسایی و سوابق پلیس | کارآگاهان و محققان خصوصی | متخصصان پیشگیری از زیان خرده‌فروشی | متخصصان مدیریت امنیتی | مدیران امنیتی | بازرسان و مأموران جمع‌آوری مالیات</t>
+          <t>حسابداران و حسابرسان | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | مدیران انطباق | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | بازرسان مالی | متخصصان ریسک مالی | تحلیل‌گران امنیت اطلاعات | تحلیلگران اطلاعاتی | وکلا | مدیران پیشگیری از زیان | تحلیل‌گران مدیریت | پارالیگال‌ها و دستیاران حقوقی | افسران شناسایی و سوابق پلیس | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1006,42 +1006,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Computer Systems Analysts (تحلیلگران سیستم‌های کامپیوتری)</t>
+          <t>تحلیلگران سیستم‌های کامپیوتری (Computer Systems Analysts)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Applications Analyst | Business Systems Analyst | Computer Analyst | Computer Systems Analyst | Computer Systems Consultant | IT Analyst (Information Technology Analyst) | IT Systems Analyst (Information Technology Systems Analyst) | Information Systems Analyst (ISA) | Programmer Analyst | Systems Analyst</t>
+          <t>تحلیل‌گر نرم‌افزارهای کاربردی | تحلیل‌گر سامانه‌های کسب‌وکار | تحلیل‌گر رایانه | تحلیل‌گر سامانه‌های رایانه‌ای | مشاور سامانه‌های رایانه‌ای | تحلیل‌گر فناوری اطلاعات (IT) | تحلیل‌گر سامانه‌های فناوری اطلاعات (IT) | تحلیل‌گر سامانه‌های اطلاعاتی (ISA) | تحلیل‌گر برنامه‌نویس | تحلیل‌گر سیستم‌ها</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3M Post-it App | ADP Workforce Now | AJAX | نرم‌افزار مدیریت دسترسی | AcmeStudio | نرم‌افزار دایرکتوری فعال | Ada | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe Photoshop | Advanced business application programming ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | Amazon Web Services AWS software | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه | زبان توصیف معماری ADL | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | نرم‌افزار سیستم هوش تجاری | C | C# | C++ | Cascading style sheets CSS | Chef | Cisco Systems CiscoWorks | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان برنامه‌نویسی COBOL | نرم‌افزار تست سازگاری | نرم‌افزار مدل شیء کامپوننت COM | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار برآورد هزینه | CrossTec NetOp Remote Control | Customer information control system CICS | Dassault Systemes CATIA | نرم‌افزار پایگاه داده | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار نمودارکشی | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | Django | Docker | Drupal | نرم‌افزار تحلیل پویا | Dynamic hypertext markup language DHTML | ESRI ArcGIS software | Eclipse IDE | Eiffel | Elasticsearch | نرم‌افزار اتوماسیون طراحی الکترونیک EDA | نرم‌افزار مدیریت عنصر | Embarcadero JBuilder | Enterprise JavaBeans | Epic Systems | Ext JS | Extensible hypertext markup language XHTML | Extensible markup language XML | FileMaker Pro | نرم‌افزار فلوچارت | زبان برنامه‌نویسی FORTRAN | نرم‌افزار تست عملکردی | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | Healthcare common procedure coding system HCPCS | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | Hierarchical simulation program with integrated circuit emphasis HSPICE | نرم‌افزار مدیریت منابع انسانی HRMS | HyperSpace | Hypertext markup language HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | IBM Power Systems software | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | Informatica Corporation PowerCenter | InstallShield | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | نرم‌افزار تست قابلیت همکاری | J | JUnit | JavaScript | JavaScript Object Notation JSON | Job control language JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | Linux | نرم‌افزار تست بار | MEDITECH software | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه پزشکی | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure software | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار تست مهاجرت | Minitab | MongoDB | نرم‌افزار تست جهش | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | Network intrusion prevention systems NIPS | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Omni Group OmniGraffle | OpenAI ChatGPT | OrCAD Capture | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle Master Data Management MDM Suite | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle SQL Developer | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | نرم‌افزار مدیریت وصله و به‌روزرسانی | Perforce Helix software | Perl | نرم‌افزار تشخیص کامپیوتر شخصی | Popkin System Architect | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Rapide | React | نرم‌افزار تست بازیابی | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل از راه دور | نرم‌افزار مدیریت الزامات | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP BusinessObjects Desktop Intelligence | SAP Crystal Reports | SAP ERP | SAP Master Data Management MDM | SAP NetWeaver | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | نرم‌افزار تست امنیت | Selenium | ServiceNow | Shell script | Skype | Slack | Slido interaction software | Smalltalk | Snort | نرم‌افزار مدیریت دارایی نرم‌افزار SAM | نرم‌افزار توزیع نرم‌افزار | SpectraQuest | Splunk Enterprise | Spring Boot | Spring Framework | Stac Software ReachOut | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار تست استرس | نرم‌افزار پیش‌بینی ساختار | Structured query language SQL | Sun Microsystems Sun ONE | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Swift | Symantec Visual Cafe | Symantec pcAnywhere | نرم‌افزار بازیابی فاجعه سیستم و داده | نرم‌افزار تست سیستم | نرم‌افزار استقرار و مهاجرت سیستم و برنامه | Tableau | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار پیاده‌سازی تست | The MathWorks MATLAB | Time sharing option TSO software | Transact-SQL | UNIX | UNIX Shell | Ubuntu | Unified modeling language UML | نرم‌افزار تست واحد | نرم‌افزار تست قابلیت استفاده | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم پروتکل صوتی روی اینترنت VoIP | نرم‌افزار سرور وب | WebFOCUS | Wireshark | Wise Solutions Wise for Windows Installer | YouTube | jQuery</t>
+          <t>3M Post-it App | ADP Workforce Now | AJAX | نرم‌افزار مدیریت دسترسی | AcmeStudio | نرم‌افزار اکتیو دایرکتوری | Ada | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | زبان توصیف معماری ADL | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | Backbone.js | Bash | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | نرم‌افزار سیستم هوش تجاری | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chef | Cisco Systems CiscoWorks | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان مشترک تجاری COBOL | نرم‌افزار تست سازگاری | نرم‌افزار مدل شیء کامپوننت COM | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار برآورد هزینه | CrossTec NetOp Remote Control | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | نرم‌افزار پایگاه داده | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار نمودارکشی | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | Django | Docker | Drupal | نرم‌افزار تحلیل پویا | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | نرم‌افزار اتوماسیون طراحی الکترونیکی EDA | نرم‌افزار مدیریت عناصر | Embarcadero JBuilder | Enterprise JavaBeans | Epic Systems | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار نمودار جریان | Formula translation/translator FORTRAN | نرم‌افزار تست عملکردی | نرم‌افزار حسابداری صندوق | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | Google Docs | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | Hierarchical simulation program with integrated circuit emphasis HSPICE | نرم‌افزار مدیریت منابع انسانی HRMS | HyperSpace | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | Informatica Corporation PowerCenter | InstallShield | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | نرم‌افزار تست تعامل‌پذیری | J | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | Linux | نرم‌افزار تست بارگذاری | نرم‌افزار MEDITECH | Marketo Marketing Automation | McAfee | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Power BI | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | نرم‌افزار تست مهاجرت | Minitab | MongoDB | نرم‌افزار تست جهش | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | سیستم‌های پیشگیری از نفوذ شبکه NIPS | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Objective C | Omni Group OmniGraffle | OpenAI ChatGPT | OrCAD Capture | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle Master Data Management MDM Suite | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle SQL Developer | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار Perforce Helix | Perl | نرم‌افزار عیب‌یابی کامپیوتر شخصی | Popkin System Architect | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | Rapide | React | نرم‌افزار تست بازیابی | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل از راه دور | نرم‌افزار مدیریت الزامات | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP BusinessObjects Desktop Intelligence | SAP Crystal Reports | SAP ERP | SAP Master Data Management MDM | SAP NetWeaver | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | نرم‌افزار تست امنیت | Selenium | ServiceNow | Shell script | Skype | Slack | نرم‌افزار تعاملی Slido | Smalltalk | Snort | نرم‌افزار مدیریت دارایی نرم‌افزار SAM | نرم‌افزار توزیع نرم‌افزار | SpectraQuest | Splunk Enterprise | Spring Boot | Spring Framework | Stac Software ReachOut | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار تست استرس | نرم‌افزار پیش‌بینی ساختار | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Sun ONE | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Visual Cafe | Symantec pcAnywhere | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار تست سیستم | نرم‌افزار استقرار و مهاجرت سیستم و برنامه | Tableau | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار اجرای تست | The MathWorks MATLAB | Time sharing option TSO software | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | نرم‌افزار تست واحد | نرم‌افزار تست کاربردپذیری | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار اسکن ویروس | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | نرم‌افزار وب سرور | WebFOCUS | Wireshark | Wise Solutions Wise for Windows Installer | YouTube | jQuery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>صحبت کردن | درک مطلب | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | نوشتن | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شنیداری | درک نوشتاری | بیان شفاهی | نظم‌دهی اطلاعات | استدلال استقرایی | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | تجسم | انعطاف‌پذیری بستار | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی | خلاقیت | دید دور</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تجسم | انعطاف‌پذیری بستار | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی | اصالت | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | بحث‌های حضوری با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | اهمیت تکرار وظایف مشابه | نتایج کاری و خروجی‌های سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای انجام حرکات تکراری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربر کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | متخصصان انفورماتیک سلامت | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیلگران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | متخصصان انفورماتیک سلامت | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0011_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0011_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم زمان و انجام همزمان امور | تجسم فضایی | به‌خاطرسپاری | استدلال ریاضی | توانایی کار با اعداد | سرعت ادراک | انعطاف‌پذیری در بستن الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | برنامه‌ریزان تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | مدیران تطبیق و انطباق | تحلیل‌گران اعتباری | بازرسان و ارزیابان مالی | مدیران مالی | تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک بیمه) | مدیران صندوق‌های سرمایه‌گذاری | مدیران پیشگیری از خسارت و اتلاف منابع | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و کارشناسان بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی شخصی | مدیران امور مقرراتی و تطبیق | کارشناسان امور مقرراتی و تطبیق | کارشناسان پیشگیری از خسارت در فروشگاه‌ها | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
+          <t>حسابداران و حسابرسان | کارشناسان برنامه‌ریزی تداوم کسب‌وکار | تحلیل‌گران هوش تجاری | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران اعتبارات و تسهیلات | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | مدیران صندوق‌های سرمایه‌گذاری | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی فردی | مدیران امور انطباق مقرراتی و حقوقی صنایع | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اقتصاد و حسابداری | حقوق و مقررات دولتی | ریاضیات | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | اقتصاد و حسابداری | قانون و دولت | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان کتبی | حساسیت به مسئله | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری در بستن الگوها | توانایی کار با اعداد | سرعت بستن الگوها | ابتکار و اصالت | روانی ایده‌ها | سرعت ادراک</t>
+          <t>درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | استدلال ریاضی | توجه انتخابی | انعطاف‌پذیری بستار | توانایی عددی | سرعت بستار | اصالت | روانی ایده‌ها | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و حسابرسی | تحلیل‌گران بودجه | مدیران ارشد اجرایی | کارشناسان جبران خدمت، مزایا و آنالیز شغل | مدیران تطبیق و انطباق | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مصاحبه‌کنندگان و بررسی‌کنندگان واجدین شرایط برنامه‌های دولتی | مدیران مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان بازرسی، کشف و تحلیل تقلب | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | تحلیل‌گران مدیریت | مشاوران مالی شخصی | مدیران حراست و امنیت | ممیزان، ماموران وصول و کارشناسان مالیاتی | خزانه‌داران و مدیران مالی (کنترلرها)</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | مدیران عامل و مدیران ارشد اجرایی | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مدیران امور مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان بازرسی، کشف و تحلیل تقلب | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان تحلیل مدیریت و روش‌ها | مشاوران مالی فردی | مدیران حراست و انتظامات | ممیزان، ماموران وصول و کارشناسان مالیاتی | خزانه‌داران و مدیران مالی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | امور اداری و دفتری | آموزش و تدریس | اقتصاد و حسابداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | اقتصاد و حسابداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | وضوح گفتار | توانایی کار با اعداد | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | توانایی عددی | استدلال ریاضی | روانی ایده‌ها | توجه انتخابی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مأموران وصول مطالبات و وصول چک | کارمندان دفترداری، حسابداری و حسابرسی | مددکاران اجتماعی کودک، خانواده و مدارس | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان و بررسی‌کنندگان واجدین شرایط برنامه‌های دولتی | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه | نمایندگان و کارشناسان فروش بیمه | مصاحبه‌کنندگان و متصدیان پرونده‌های تسهیلاتی | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی شخصی | مشاوران توان‌بخشی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | مددکاران اجتماعی کودک، خانواده و مدرسه | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | متصدیان افتتاح حساب | مشاوران مالی فردی | مشاوران توانبخشی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | ریاضیات | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | حقوق و مقررات دولتی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی کار با اعداد | مرتب‌سازی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | توانایی عددی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مأموران وصول مطالبات و وصول چک | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | مدیران مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک بیمه) | مصاحبه‌کنندگان و متصدیان پرونده‌های تسهیلاتی | متصدیان افتتاح حساب | مشاوران مالی شخصی | کارگزاران و مشاوران املاک | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | بازرسان و ارزیابان مالی | مدیران امور مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان پذیرش و امور اداری تسهیلات و وام | متصدیان افتتاح حساب | مشاوران مالی فردی | کارگزاران و مدیران معاملات املاک | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | امور اداری و دفتری | حقوق و مقررات دولتی | اقتصاد و حسابداری | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | قانون و دولت | اقتصاد و حسابداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | توانایی کار با اعداد | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری در بستن الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بیان کتبی | توانایی عددی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مأموران وصول مطالبات و وصول چک | متصدیان صدور و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و حسابرسی | تحلیل‌گران بودجه | ارزیابان، کارشناسان و بازرسان خسارت بیمه | کارشناسان نظارت و تطبیق | کارمندان امور نامه‌نگاری و مکاتبات اداری | کارمندان دادگاه، شهرداری و صدور پروانه‌ها | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان و بررسی‌کنندگان واجدین شرایط برنامه‌های دولتی | بازرسان و ارزیابان مالی | کارمندان پردازش خسارت و بیمه‌نامه | کارشناسان و مسئولان تسهیلات و اعتبارات | کارمندان حقوق و دستمزد و ثبت زمان کارکرد | مشاوران مالی شخصی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | کارشناسان و مسئولان تسهیلات و اعتبارات | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | حقوق و مقررات دولتی | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | توانایی کار با اعداد | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری در بستن الگوها | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بیان کتبی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | توانایی عددی | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | استدلال ریاضی | حساسیت به مسئله | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | متصدیان صدور و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | تحلیل‌گران بودجه | کارشناسان جبران خدمت، مزایا و آنالیز شغل | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مشاوران اعتباری و مدیریت بدهی | مصاحبه‌کنندگان و بررسی‌کنندگان واجدین شرایط برنامه‌های دولتی | بازرسان و ارزیابان مالی | مدیران مالی | کارمندان پردازش خسارت و بیمه‌نامه | دبیران حقوقی و دستیاران اداری | مصاحبه‌کنندگان و متصدیان پرونده‌های تسهیلاتی | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان حقوقی و دستیاران وکالت | کارمندان حقوق و دستمزد و ثبت زمان کارکرد | مشاوران مالی شخصی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | تحلیل‌گران بودجه | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان و ارزیابان مالی | مدیران امور مالی | کارمندان پردازش خسارت و بیمه‌نامه‌ها | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | کارشناسان و دستیاران امور حقوقی | کارمندان امور حقوق، دستمزد و ثبت زمان | مشاوران مالی فردی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | امور اداری، کارکنان و منابع انسانی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی | فروش و بازاریابی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تسهیم زمان و انجام همزمان امور | تجسم فضایی | به‌خاطرسپاری | استدلال ریاضی | توانایی کار با اعداد | سرعت ادراک | انعطاف‌پذیری در بستن الگوها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تحلیل‌گران کمّی مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران مالی و سرمایه‌گذاری | مشاوران مالی شخصی | کارشناسان ریسک مالی | تحلیل‌گران بودجه | تحلیل‌گران اعتباری | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک بیمه) | بازرسان و ارزیابان مالی | مشاوران اعتباری و مدیریت بدهی | کارشناسان و مسئولان تسهیلات و اعتبارات | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | حسابداران و حسابرسان | کارشناسان ارزیابی و قیمت‌گذاری املاک | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | مدیران مالی | خزانه‌داران و مدیران مالی (کنترلرها) | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت</t>
+          <t>تحلیل‌گران کمّی مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران مالی و سرمایه‌گذاری | مشاوران مالی فردی | کارشناسان ریسک مالی | تحلیل‌گران بودجه | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | بازرسان و ارزیابان مالی | مشاوران اعتباری و مدیریت بدهی | کارشناسان و مسئولان تسهیلات و اعتبارات | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی | حسابداران و حسابرسان | کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | مدیران امور مالی | خزانه‌داران و مدیران مالی | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | شنیدن فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | توانایی کار با اعداد | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | ابتکار و اصالت</t>
+          <t>استدلال ریاضی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | توانایی عددی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اکچوئریست‌ها (کارشناسان محاسبات فنی بیمه) | متخصصان آمار زیستی | تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران اعتباری | دانشمندان داده | متخصصان انبار داده | معماران پایگاه داده | اقتصاددانان | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و کارشناسان بازاریابی | تحلیل‌گران تحقیق در عملیات | کارشناسان آزمون نفوذپذیری | مشاوران مالی شخصی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران آماری | متخصصان آمار</t>
+          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران اعتبارات و تسهیلات | دانشمندان داده | متخصصان انباره داده | معماران پایگاه داده | اقتصاددانان | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | مشاوران مالی فردی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و امور اداری | ریاضیات | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات | خدمات مشتری و شخصی | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستن الگوها | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | روانی ایده‌ها</t>
+          <t>بیان کتبی | درک شفاهی | حساسیت به مسئله | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | ارزیابان، کارشناسان و بازرسان خسارت بیمه | مدیران تطبیق و انطباق | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال (فورنزیک دیجیتال) | بازرسان و ارزیابان مالی | کارشناسان ریسک مالی | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران اطلاعاتی و امنیتی | وکلا | مدیران پیشگیری از خسارت و اتلاف منابع | تحلیل‌گران مدیریت | کارشناسان حقوقی و دستیاران وکالت | افسران تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از خسارت در فروشگاه‌ها | کارشناسان مدیریت امنیت | مدیران حراست و امنیت | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مدیران تطبیق و نظارت مقرراتی | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | بازرسان و ارزیابان مالی | کارشناسان ریسک مالی | تحلیل‌گران امنیت اطلاعات | تحلیل‌گران داده‌ها و اطلاعات امنیتی | وکلا | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و دستیاران امور حقوقی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | شنیدن فعال | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال استقرایی | دید نزدیک | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | انعطاف‌پذیری در بستن الگوها | سرعت ادراک | سرعت بستن الگوها | توانایی کار با اعداد | استدلال ریاضی | ابتکار و اصالت | دید دور</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال استقرایی | بینایی نزدیک | حساسیت به مسئله | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تجسم | انعطاف‌پذیری بستار | سرعت ادراکی | سرعت بستار | توانایی عددی | استدلال ریاضی | اصالت | بینایی دور</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه‌های کامپیوتری | کارشناسان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | مهندسان و معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | مدیران فناوری اطلاعات و سیستم‌های کامپیوتری | دانشمندان داده | متخصصان انبار داده | مدیران پایگاه داده (DBA) | معماران پایگاه داده | متخصصان مدیریت اسناد و مدارک | متخصصان انفورماتیک سلامت | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذپذیری | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متخصصان انفورماتیک سلامت | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
